--- a/data/trans_orig/CLASESOCIAL_R2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/CLASESOCIAL_R2-Clase-trans_orig.xlsx
@@ -4123,7 +4123,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>599812</t>
+          <t>603883</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>697472</t>
+          <t>695898</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1758722</t>
+          <t>1756835</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1874330</t>
+          <t>1872386</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2386371</t>
+          <t>2389734</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>2546137</t>
+          <t>2548391</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,33%</t>
         </is>
       </c>
     </row>
@@ -4938,12 +4938,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1177587</t>
+          <t>1182260</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>1295040</t>
+          <t>1291882</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4953,12 +4953,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4973,12 +4973,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>669763</t>
+          <t>668407</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>761631</t>
+          <t>764210</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4988,12 +4988,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5008,12 +5008,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1877946</t>
+          <t>1884986</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>2030559</t>
+          <t>2031048</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5023,12 +5023,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,55%</t>
         </is>
       </c>
     </row>
@@ -5051,12 +5051,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>502803</t>
+          <t>499735</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>587079</t>
+          <t>586623</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5066,12 +5066,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>142595</t>
+          <t>146100</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>194139</t>
+          <t>193396</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5101,12 +5101,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>661531</t>
+          <t>664154</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>763155</t>
+          <t>763618</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,49%</t>
         </is>
       </c>
     </row>
@@ -5164,12 +5164,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>332112</t>
+          <t>329431</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>405521</t>
+          <t>403656</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5179,12 +5179,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>338076</t>
+          <t>335875</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>412182</t>
+          <t>408246</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5214,12 +5214,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>689070</t>
+          <t>689287</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>795843</t>
+          <t>790287</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5249,12 +5249,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,89%</t>
         </is>
       </c>
     </row>
@@ -5277,12 +5277,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>435160</t>
+          <t>432486</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>516845</t>
+          <t>515032</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5292,12 +5292,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>278822</t>
+          <t>273465</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>342619</t>
+          <t>340539</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>730490</t>
+          <t>736393</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>841847</t>
+          <t>841043</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,65%</t>
         </is>
       </c>
     </row>
@@ -9131,7 +9131,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>730082</t>
+          <t>727225</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>831846</t>
+          <t>826414</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1802337</t>
+          <t>1816965</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1927299</t>
+          <t>1934178</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2566804</t>
+          <t>2565143</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>2737270</t>
+          <t>2735389</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>39,23%</t>
         </is>
       </c>
     </row>
@@ -9946,12 +9946,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1098547</t>
+          <t>1102393</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>1213518</t>
+          <t>1211433</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9961,12 +9961,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9981,12 +9981,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>717585</t>
+          <t>714189</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>818227</t>
+          <t>813292</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10016,12 +10016,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1851860</t>
+          <t>1849598</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>2013927</t>
+          <t>2013237</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,88%</t>
         </is>
       </c>
     </row>
@@ -10059,12 +10059,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>583397</t>
+          <t>585274</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>675684</t>
+          <t>676652</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10094,12 +10094,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>231269</t>
+          <t>232308</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>292526</t>
+          <t>296691</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>831079</t>
+          <t>830943</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>953851</t>
+          <t>945163</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10149,7 +10149,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,56%</t>
         </is>
       </c>
     </row>
@@ -10172,12 +10172,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>379269</t>
+          <t>380428</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>461909</t>
+          <t>465860</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10187,12 +10187,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>301749</t>
+          <t>300467</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>374524</t>
+          <t>375063</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10242,12 +10242,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>702236</t>
+          <t>701835</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>812977</t>
+          <t>812347</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,65%</t>
         </is>
       </c>
     </row>
@@ -10285,12 +10285,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>397051</t>
+          <t>399381</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>480075</t>
+          <t>480162</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10300,7 +10300,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>280093</t>
+          <t>279966</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>353175</t>
+          <t>355128</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10340,7 +10340,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>699548</t>
+          <t>699730</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>808753</t>
+          <t>811759</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,64%</t>
         </is>
       </c>
     </row>
@@ -14139,7 +14139,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -14841,12 +14841,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>852444</t>
+          <t>854347</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>961037</t>
+          <t>958562</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14856,12 +14856,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14876,12 +14876,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1758303</t>
+          <t>1758090</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1875817</t>
+          <t>1883523</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14891,12 +14891,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14911,12 +14911,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2642453</t>
+          <t>2657679</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>2803331</t>
+          <t>2820917</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14926,12 +14926,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,78%</t>
         </is>
       </c>
     </row>
@@ -14954,12 +14954,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1099546</t>
+          <t>1093665</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>1207276</t>
+          <t>1208147</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14969,12 +14969,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14989,12 +14989,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>775947</t>
+          <t>770458</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>877477</t>
+          <t>881597</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15004,12 +15004,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15024,12 +15024,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1899822</t>
+          <t>1899860</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>2053917</t>
+          <t>2049061</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15039,12 +15039,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,62%</t>
         </is>
       </c>
     </row>
@@ -15067,12 +15067,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>479151</t>
+          <t>480099</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>565326</t>
+          <t>564909</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15082,12 +15082,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15102,12 +15102,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>140483</t>
+          <t>142216</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>194903</t>
+          <t>195283</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15117,12 +15117,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15137,12 +15137,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>638827</t>
+          <t>637212</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>737815</t>
+          <t>742649</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15152,12 +15152,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,74%</t>
         </is>
       </c>
     </row>
@@ -15180,12 +15180,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>341358</t>
+          <t>339123</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>414341</t>
+          <t>416923</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15195,12 +15195,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15215,12 +15215,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>334751</t>
+          <t>332832</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>407293</t>
+          <t>406402</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15230,47 +15230,47 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
+          <t>11,51%</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>706</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>749500</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>693017</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>797334</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>10,84%</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>10,02%</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
           <t>11,53%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>706</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>749500</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>702156</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>803740</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>10,84%</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t>10,15%</t>
-        </is>
-      </c>
-      <c r="W43" s="2" t="inlineStr">
-        <is>
-          <t>11,62%</t>
         </is>
       </c>
     </row>
@@ -15293,12 +15293,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>391180</t>
+          <t>391509</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>470225</t>
+          <t>473244</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15308,12 +15308,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15328,12 +15328,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>312589</t>
+          <t>313787</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>384354</t>
+          <t>385101</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15343,12 +15343,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15363,12 +15363,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>718318</t>
+          <t>722601</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>831543</t>
+          <t>828594</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15378,12 +15378,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,98%</t>
         </is>
       </c>
     </row>
@@ -16204,7 +16204,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -16239,7 +16239,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -16274,7 +16274,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -16317,17 +16317,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -16352,17 +16352,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -16387,17 +16387,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -16773,7 +16773,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -16808,7 +16808,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -16843,7 +16843,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -16999,17 +16999,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -17034,17 +17034,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -17069,17 +17069,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -17342,7 +17342,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -17377,7 +17377,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -17412,7 +17412,7 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
@@ -17681,17 +17681,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -17716,17 +17716,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -17751,17 +17751,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -17911,7 +17911,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -17946,7 +17946,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -17981,7 +17981,7 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
@@ -18363,17 +18363,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -18398,17 +18398,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -18433,17 +18433,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -18480,7 +18480,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -18515,7 +18515,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -18550,7 +18550,7 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
@@ -19045,17 +19045,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -19080,17 +19080,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -19115,17 +19115,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -19147,7 +19147,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -19162,7 +19162,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -19197,7 +19197,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -19232,7 +19232,7 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
@@ -19727,17 +19727,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -19762,17 +19762,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -19797,17 +19797,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -19844,32 +19844,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>715553</t>
+          <t>805191</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>558054</t>
+          <t>745932</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>798667</t>
+          <t>863694</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -19879,32 +19879,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>1602706</t>
+          <t>1675131</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1319407</t>
+          <t>1625439</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1745884</t>
+          <t>1733236</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -19914,32 +19914,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>2318259</t>
+          <t>2480322</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2012993</t>
+          <t>2398486</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>2512459</t>
+          <t>2559098</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>36,16%</t>
         </is>
       </c>
     </row>
@@ -19957,32 +19957,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>832568</t>
+          <t>1071477</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>1138250</t>
+          <t>1192355</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -19992,32 +19992,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>797487</t>
+          <t>808974</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>1443812</t>
+          <t>905209</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -20027,32 +20027,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1785660</t>
+          <t>1917618</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>2528159</t>
+          <t>2070074</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>29,25%</t>
         </is>
       </c>
     </row>
@@ -20070,32 +20070,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>446255</t>
+          <t>427764</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1182023</t>
+          <t>513546</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -20105,32 +20105,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>138341</t>
+          <t>165094</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>192324</t>
+          <t>211943</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -20140,32 +20140,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>597315</t>
+          <t>612036</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1560612</t>
+          <t>704802</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>9,96%</t>
         </is>
       </c>
     </row>
@@ -20183,32 +20183,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>452212</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>350311</t>
+          <t>441755</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>504194</t>
+          <t>525298</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -20218,32 +20218,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>315803</t>
+          <t>388308</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>430409</t>
+          <t>458128</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -20253,32 +20253,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>723036</t>
+          <t>855894</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>912867</t>
+          <t>967276</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,67%</t>
         </is>
       </c>
     </row>
@@ -20296,32 +20296,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>406553</t>
+          <t>506378</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>559730</t>
+          <t>595163</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -20331,32 +20331,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>366576</t>
+          <t>454669</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>500562</t>
+          <t>526165</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
+          <t>13,43%</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
           <t>12,51%</t>
         </is>
       </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>10,25%</t>
-        </is>
-      </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -20366,32 +20366,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>823207</t>
+          <t>979808</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1033864</t>
+          <t>1094404</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,46%</t>
         </is>
       </c>
     </row>
@@ -20409,17 +20409,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -20444,17 +20444,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -20479,17 +20479,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
